--- a/C/chrVI:0-45026_23_finemapping.xlsx
+++ b/C/chrVI:0-45026_23_finemapping.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4269" uniqueCount="4269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4261" uniqueCount="4261">
   <si>
     <t xml:space="preserve">DATA</t>
   </si>
@@ -12224,19 +12224,10 @@
     <t xml:space="preserve">in.hotspot</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.x</t>
-  </si>
-  <si>
     <t xml:space="preserve">bin_pos_l</t>
   </si>
   <si>
-    <t xml:space="preserve">Beta.y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE.y</t>
+    <t xml:space="preserve">SE</t>
   </si>
   <si>
     <t xml:space="preserve">chrom_short</t>
@@ -12477,21 +12468,6 @@
   </si>
   <si>
     <t xml:space="preserve">RPS14A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G2:M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_M:G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_G1:S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z_S</t>
   </si>
   <si>
     <t xml:space="preserve">cis_fdr</t>
@@ -13257,48 +13233,42 @@
         <v>4066</v>
       </c>
       <c r="Z1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA1" t="s">
         <v>4067</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>4068</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>4069</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE1" t="s">
         <v>4070</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>4071</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>4072</v>
       </c>
-      <c r="AF1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>4073</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>4074</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>4075</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>4076</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>4078</v>
+        <v>4075</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -13352,62 +13322,60 @@
         <v>30041</v>
       </c>
       <c r="U2" t="s">
-        <v>4079</v>
+        <v>4076</v>
       </c>
       <c r="V2" t="n">
         <v>17457</v>
       </c>
       <c r="W2" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X2" t="b">
         <v>1</v>
       </c>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB2" t="n">
+      <c r="Y2" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z2" t="n">
         <v>-1.83180269874678</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AA2" t="n">
         <v>0.320536769808738</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>4079</v>
       </c>
       <c r="AD2" t="s">
         <v>19</v>
       </c>
       <c r="AE2" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>4083</v>
+        <v>4079</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>4080</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>4084</v>
+        <v>4081</v>
       </c>
       <c r="D3" t="s">
-        <v>4085</v>
+        <v>4082</v>
       </c>
       <c r="E3" t="n">
         <v>43976</v>
@@ -13458,62 +13426,60 @@
         <v>43976</v>
       </c>
       <c r="U3" t="s">
-        <v>4086</v>
+        <v>4083</v>
       </c>
       <c r="V3" t="n">
         <v>554396</v>
       </c>
       <c r="W3" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X3" t="b">
         <v>1</v>
       </c>
-      <c r="Y3"/>
-      <c r="Z3"/>
-      <c r="AA3" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="Y3" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z3" t="n">
         <v>0.587754648088531</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AA3" t="n">
         <v>0.179695039677822</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>4084</v>
       </c>
       <c r="AD3" t="s">
         <v>19</v>
       </c>
       <c r="AE3" t="s">
-        <v>4087</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>4087</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>4088</v>
+        <v>4084</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>4085</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>4089</v>
+        <v>4086</v>
       </c>
       <c r="D4" t="s">
-        <v>4090</v>
+        <v>4087</v>
       </c>
       <c r="E4" t="n">
         <v>7689</v>
@@ -13564,62 +13530,60 @@
         <v>18841</v>
       </c>
       <c r="U4" t="s">
-        <v>4079</v>
+        <v>4076</v>
       </c>
       <c r="V4" t="n">
         <v>1802</v>
       </c>
       <c r="W4" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X4" t="b">
         <v>1</v>
       </c>
-      <c r="Y4"/>
-      <c r="Z4"/>
-      <c r="AA4" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="Y4" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z4" t="n">
         <v>-1.03967984195971</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AA4" t="n">
         <v>0.332215338062465</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>4079</v>
       </c>
       <c r="AD4" t="s">
         <v>19</v>
       </c>
       <c r="AE4" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>4091</v>
+        <v>4079</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>4088</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>4092</v>
+        <v>4089</v>
       </c>
       <c r="D5" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E5" t="n">
         <v>7689</v>
@@ -13670,62 +13634,60 @@
         <v>7689</v>
       </c>
       <c r="U5" t="s">
-        <v>4094</v>
+        <v>4091</v>
       </c>
       <c r="V5" t="n">
         <v>302680</v>
       </c>
       <c r="W5" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X5" t="b">
         <v>1</v>
       </c>
-      <c r="Y5"/>
-      <c r="Z5"/>
-      <c r="AA5" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="Y5" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z5" t="n">
         <v>-0.174274461837799</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AA5" t="n">
         <v>0.0605459542093644</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>4092</v>
       </c>
       <c r="AD5" t="s">
         <v>19</v>
       </c>
       <c r="AE5" t="s">
-        <v>4095</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG5" t="s">
-        <v>4095</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="s">
-        <v>4096</v>
+        <v>4092</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>4093</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>4097</v>
+        <v>4094</v>
       </c>
       <c r="D6" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E6" t="n">
         <v>7689</v>
@@ -13776,62 +13738,60 @@
         <v>7689</v>
       </c>
       <c r="U6" t="s">
-        <v>4098</v>
+        <v>4095</v>
       </c>
       <c r="V6" t="n">
         <v>45978</v>
       </c>
       <c r="W6" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X6" t="b">
         <v>1</v>
       </c>
-      <c r="Y6"/>
-      <c r="Z6"/>
-      <c r="AA6" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="Y6" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z6" t="n">
         <v>-0.137247511287776</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AA6" t="n">
         <v>0.0500806482030786</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>4096</v>
       </c>
       <c r="AD6" t="s">
         <v>19</v>
       </c>
       <c r="AE6" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG6" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="s">
-        <v>4100</v>
+        <v>4096</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>4097</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>4101</v>
+        <v>4098</v>
       </c>
       <c r="D7" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E7" t="n">
         <v>7689</v>
@@ -13882,62 +13842,60 @@
         <v>7689</v>
       </c>
       <c r="U7" t="s">
-        <v>4102</v>
+        <v>4099</v>
       </c>
       <c r="V7" t="n">
         <v>85676</v>
       </c>
       <c r="W7" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X7" t="b">
         <v>1</v>
       </c>
-      <c r="Y7"/>
-      <c r="Z7"/>
-      <c r="AA7" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="Y7" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z7" t="n">
         <v>-0.274073243176674</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AA7" t="n">
         <v>0.0968816125120023</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>4100</v>
       </c>
       <c r="AD7" t="s">
         <v>19</v>
       </c>
       <c r="AE7" t="s">
-        <v>4103</v>
-      </c>
-      <c r="AF7" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG7" t="s">
-        <v>4103</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>4104</v>
+        <v>4100</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>4101</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>4105</v>
+        <v>4102</v>
       </c>
       <c r="D8" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E8" t="n">
         <v>7689</v>
@@ -13988,62 +13946,60 @@
         <v>7689</v>
       </c>
       <c r="U8" t="s">
-        <v>4098</v>
+        <v>4095</v>
       </c>
       <c r="V8" t="n">
         <v>300166</v>
       </c>
       <c r="W8" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X8" t="b">
         <v>1</v>
       </c>
-      <c r="Y8"/>
-      <c r="Z8"/>
-      <c r="AA8" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="Y8" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z8" t="n">
         <v>-0.205456038028267</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AA8" t="n">
         <v>0.0725355657612296</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>4096</v>
       </c>
       <c r="AD8" t="s">
         <v>19</v>
       </c>
       <c r="AE8" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG8" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>4106</v>
+        <v>4096</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>4103</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>4107</v>
+        <v>4104</v>
       </c>
       <c r="D9" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E9" t="n">
         <v>7689</v>
@@ -14094,62 +14050,60 @@
         <v>7689</v>
       </c>
       <c r="U9" t="s">
-        <v>4094</v>
+        <v>4091</v>
       </c>
       <c r="V9" t="n">
         <v>493793</v>
       </c>
       <c r="W9" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X9" t="b">
         <v>1</v>
       </c>
-      <c r="Y9"/>
-      <c r="Z9"/>
-      <c r="AA9" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="Y9" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z9" t="n">
         <v>-0.188631803350871</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AA9" t="n">
         <v>0.0685204676090515</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>4092</v>
       </c>
       <c r="AD9" t="s">
         <v>19</v>
       </c>
       <c r="AE9" t="s">
-        <v>4095</v>
-      </c>
-      <c r="AF9" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG9" t="s">
-        <v>4095</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>4108</v>
+        <v>4092</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>4105</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>4109</v>
+        <v>4106</v>
       </c>
       <c r="D10" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E10" t="n">
         <v>7689</v>
@@ -14200,62 +14154,60 @@
         <v>7689</v>
       </c>
       <c r="U10" t="s">
-        <v>4098</v>
+        <v>4095</v>
       </c>
       <c r="V10" t="n">
         <v>168423</v>
       </c>
       <c r="W10" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X10" t="b">
         <v>1</v>
       </c>
-      <c r="Y10"/>
-      <c r="Z10"/>
-      <c r="AA10" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB10" t="n">
+      <c r="Y10" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z10" t="n">
         <v>-0.132610037338247</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AA10" t="n">
         <v>0.0608385536773679</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>4096</v>
       </c>
       <c r="AD10" t="s">
         <v>19</v>
       </c>
       <c r="AE10" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AF10" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG10" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ10" t="s">
-        <v>4110</v>
+        <v>4096</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>4107</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>4111</v>
+        <v>4108</v>
       </c>
       <c r="D11" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E11" t="n">
         <v>7689</v>
@@ -14306,62 +14258,60 @@
         <v>7689</v>
       </c>
       <c r="U11" t="s">
-        <v>4112</v>
+        <v>4109</v>
       </c>
       <c r="V11" t="n">
         <v>654166</v>
       </c>
       <c r="W11" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X11" t="b">
         <v>1</v>
       </c>
-      <c r="Y11"/>
-      <c r="Z11"/>
-      <c r="AA11" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="Y11" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z11" t="n">
         <v>-0.169479037321107</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AA11" t="n">
         <v>0.061737591383179</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>4110</v>
       </c>
       <c r="AD11" t="s">
         <v>19</v>
       </c>
       <c r="AE11" t="s">
-        <v>4113</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG11" t="s">
-        <v>4113</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>4114</v>
+        <v>4110</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>4111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>4115</v>
+        <v>4112</v>
       </c>
       <c r="D12" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E12" t="n">
         <v>7689</v>
@@ -14412,62 +14362,60 @@
         <v>7689</v>
       </c>
       <c r="U12" t="s">
-        <v>4116</v>
+        <v>4113</v>
       </c>
       <c r="V12" t="n">
         <v>368781</v>
       </c>
       <c r="W12" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X12" t="b">
         <v>1</v>
       </c>
-      <c r="Y12"/>
-      <c r="Z12"/>
-      <c r="AA12" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="Y12" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z12" t="n">
         <v>-0.255227170822943</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AA12" t="n">
         <v>0.0972753400836266</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>4114</v>
       </c>
       <c r="AD12" t="s">
         <v>19</v>
       </c>
       <c r="AE12" t="s">
-        <v>4117</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG12" t="s">
-        <v>4117</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>4118</v>
+        <v>4114</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>4115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>4119</v>
+        <v>4116</v>
       </c>
       <c r="D13" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E13" t="n">
         <v>7689</v>
@@ -14518,62 +14466,60 @@
         <v>7689</v>
       </c>
       <c r="U13" t="s">
-        <v>4112</v>
+        <v>4109</v>
       </c>
       <c r="V13" t="n">
         <v>700594</v>
       </c>
       <c r="W13" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X13" t="b">
         <v>1</v>
       </c>
-      <c r="Y13"/>
-      <c r="Z13"/>
-      <c r="AA13" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="Y13" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z13" t="n">
         <v>-0.156356249492336</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AA13" t="n">
         <v>0.0568304110558157</v>
+      </c>
+      <c r="AB13" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC13" t="s">
+        <v>4110</v>
       </c>
       <c r="AD13" t="s">
         <v>19</v>
       </c>
       <c r="AE13" t="s">
-        <v>4113</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>4113</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>4120</v>
+        <v>4110</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>4117</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>4121</v>
+        <v>4118</v>
       </c>
       <c r="D14" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E14" t="n">
         <v>7689</v>
@@ -14624,62 +14570,60 @@
         <v>7689</v>
       </c>
       <c r="U14" t="s">
-        <v>4116</v>
+        <v>4113</v>
       </c>
       <c r="V14" t="n">
         <v>522663</v>
       </c>
       <c r="W14" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X14" t="b">
         <v>1</v>
       </c>
-      <c r="Y14"/>
-      <c r="Z14"/>
-      <c r="AA14" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="Y14" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z14" t="n">
         <v>-0.130696400835051</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AA14" t="n">
         <v>0.0570895339907312</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC14" t="s">
+        <v>4114</v>
       </c>
       <c r="AD14" t="s">
         <v>19</v>
       </c>
       <c r="AE14" t="s">
-        <v>4117</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="s">
-        <v>4117</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>4122</v>
+        <v>4114</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>4119</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>4123</v>
+        <v>4120</v>
       </c>
       <c r="D15" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E15" t="n">
         <v>7689</v>
@@ -14730,62 +14674,60 @@
         <v>7689</v>
       </c>
       <c r="U15" t="s">
-        <v>4124</v>
+        <v>4121</v>
       </c>
       <c r="V15" t="n">
         <v>550109</v>
       </c>
       <c r="W15" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X15" t="b">
         <v>1</v>
       </c>
-      <c r="Y15"/>
-      <c r="Z15"/>
-      <c r="AA15" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="Y15" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z15" t="n">
         <v>-0.223246913533927</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AA15" t="n">
         <v>0.0863245340218956</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC15" t="s">
+        <v>4122</v>
       </c>
       <c r="AD15" t="s">
         <v>19</v>
       </c>
       <c r="AE15" t="s">
-        <v>4125</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG15" t="s">
-        <v>4125</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>4126</v>
+        <v>4122</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="s">
+        <v>4123</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>4127</v>
+        <v>4124</v>
       </c>
       <c r="D16" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E16" t="n">
         <v>7689</v>
@@ -14836,62 +14778,60 @@
         <v>7689</v>
       </c>
       <c r="U16" t="s">
-        <v>4128</v>
+        <v>4125</v>
       </c>
       <c r="V16" t="n">
         <v>316768</v>
       </c>
       <c r="W16" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X16" t="b">
         <v>1</v>
       </c>
-      <c r="Y16"/>
-      <c r="Z16"/>
-      <c r="AA16" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="Y16" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z16" t="n">
         <v>-0.14541723673844</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AA16" t="n">
         <v>0.0667101029634459</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>4126</v>
       </c>
       <c r="AD16" t="s">
         <v>19</v>
       </c>
       <c r="AE16" t="s">
-        <v>4129</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG16" t="s">
-        <v>4129</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>4130</v>
+        <v>4126</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>4127</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>4131</v>
+        <v>4128</v>
       </c>
       <c r="D17" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E17" t="n">
         <v>7689</v>
@@ -14942,62 +14882,60 @@
         <v>7689</v>
       </c>
       <c r="U17" t="s">
-        <v>4079</v>
+        <v>4076</v>
       </c>
       <c r="V17" t="n">
         <v>579458</v>
       </c>
       <c r="W17" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X17" t="b">
         <v>1</v>
       </c>
-      <c r="Y17"/>
-      <c r="Z17"/>
-      <c r="AA17" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="Y17" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z17" t="n">
         <v>-0.19167050809923</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AA17" t="n">
         <v>0.0797936195803466</v>
+      </c>
+      <c r="AB17" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC17" t="s">
+        <v>4079</v>
       </c>
       <c r="AD17" t="s">
         <v>19</v>
       </c>
       <c r="AE17" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>4132</v>
+        <v>4079</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="s">
+        <v>4129</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>4133</v>
+        <v>4130</v>
       </c>
       <c r="D18" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E18" t="n">
         <v>7689</v>
@@ -15048,62 +14986,60 @@
         <v>7689</v>
       </c>
       <c r="U18" t="s">
-        <v>4079</v>
+        <v>4076</v>
       </c>
       <c r="V18" t="n">
         <v>491515</v>
       </c>
       <c r="W18" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X18" t="b">
         <v>1</v>
       </c>
-      <c r="Y18"/>
-      <c r="Z18"/>
-      <c r="AA18" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB18" t="n">
+      <c r="Y18" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z18" t="n">
         <v>-0.207894968428493</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AA18" t="n">
         <v>0.0819127613263932</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>4079</v>
       </c>
       <c r="AD18" t="s">
         <v>19</v>
       </c>
       <c r="AE18" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="s">
-        <v>4134</v>
+        <v>4079</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="s">
+        <v>4131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>4135</v>
+        <v>4132</v>
       </c>
       <c r="D19" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E19" t="n">
         <v>7689</v>
@@ -15154,62 +15090,60 @@
         <v>7689</v>
       </c>
       <c r="U19" t="s">
-        <v>4079</v>
+        <v>4076</v>
       </c>
       <c r="V19" t="n">
         <v>1301616</v>
       </c>
       <c r="W19" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X19" t="b">
         <v>1</v>
       </c>
-      <c r="Y19"/>
-      <c r="Z19"/>
-      <c r="AA19" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="Y19" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z19" t="n">
         <v>-0.195632210711658</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AA19" t="n">
         <v>0.0851864893408086</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>4079</v>
       </c>
       <c r="AD19" t="s">
         <v>19</v>
       </c>
       <c r="AE19" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG19" t="s">
-        <v>4082</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>4136</v>
+        <v>4079</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="s">
+        <v>4133</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>4137</v>
+        <v>4134</v>
       </c>
       <c r="D20" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E20" t="n">
         <v>7689</v>
@@ -15260,62 +15194,60 @@
         <v>7689</v>
       </c>
       <c r="U20" t="s">
-        <v>4138</v>
+        <v>4135</v>
       </c>
       <c r="V20" t="n">
         <v>920575</v>
       </c>
       <c r="W20" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X20" t="b">
         <v>1</v>
       </c>
-      <c r="Y20"/>
-      <c r="Z20"/>
-      <c r="AA20" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="Y20" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z20" t="n">
         <v>-0.216340072196286</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AA20" t="n">
         <v>0.109425296357829</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC20" t="s">
+        <v>4136</v>
       </c>
       <c r="AD20" t="s">
         <v>19</v>
       </c>
       <c r="AE20" t="s">
-        <v>4139</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG20" t="s">
-        <v>4139</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>4140</v>
+        <v>4136</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="s">
+        <v>4137</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>4141</v>
+        <v>4138</v>
       </c>
       <c r="D21" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E21" t="n">
         <v>7689</v>
@@ -15366,62 +15298,60 @@
         <v>7689</v>
       </c>
       <c r="U21" t="s">
-        <v>4098</v>
+        <v>4095</v>
       </c>
       <c r="V21" t="n">
         <v>604508</v>
       </c>
       <c r="W21" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X21" t="b">
         <v>1</v>
       </c>
-      <c r="Y21"/>
-      <c r="Z21"/>
-      <c r="AA21" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="Y21" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z21" t="n">
         <v>-0.199396154919093</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AA21" t="n">
         <v>0.0822116100760058</v>
+      </c>
+      <c r="AB21" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC21" t="s">
+        <v>4096</v>
       </c>
       <c r="AD21" t="s">
         <v>19</v>
       </c>
       <c r="AE21" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG21" t="s">
-        <v>4099</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="s">
-        <v>4142</v>
+        <v>4096</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="s">
+        <v>4139</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>4143</v>
+        <v>4140</v>
       </c>
       <c r="D22" t="s">
-        <v>4144</v>
+        <v>4141</v>
       </c>
       <c r="E22" t="n">
         <v>7689</v>
@@ -15472,62 +15402,60 @@
         <v>19095</v>
       </c>
       <c r="U22" t="s">
-        <v>4094</v>
+        <v>4091</v>
       </c>
       <c r="V22" t="n">
         <v>372365</v>
       </c>
       <c r="W22" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X22" t="b">
         <v>1</v>
       </c>
-      <c r="Y22"/>
-      <c r="Z22"/>
-      <c r="AA22" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="Y22" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z22" t="n">
         <v>-0.407989324747951</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AA22" t="n">
         <v>0.223831364287965</v>
+      </c>
+      <c r="AB22" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC22" t="s">
+        <v>4092</v>
       </c>
       <c r="AD22" t="s">
         <v>19</v>
       </c>
       <c r="AE22" t="s">
-        <v>4095</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG22" t="s">
-        <v>4095</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI22" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="s">
-        <v>4143</v>
+        <v>4092</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="s">
+        <v>4140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>4145</v>
+        <v>4142</v>
       </c>
       <c r="D23" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E23" t="n">
         <v>7689</v>
@@ -15578,62 +15506,60 @@
         <v>7689</v>
       </c>
       <c r="U23" t="s">
-        <v>4128</v>
+        <v>4125</v>
       </c>
       <c r="V23" t="n">
         <v>98411</v>
       </c>
       <c r="W23" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X23" t="b">
         <v>1</v>
       </c>
-      <c r="Y23"/>
-      <c r="Z23"/>
-      <c r="AA23" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB23" t="n">
+      <c r="Y23" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z23" t="n">
         <v>-0.20584315908658</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AA23" t="n">
         <v>0.0862388533444943</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>4126</v>
       </c>
       <c r="AD23" t="s">
         <v>19</v>
       </c>
       <c r="AE23" t="s">
-        <v>4129</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG23" t="s">
-        <v>4129</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ23" t="s">
-        <v>4146</v>
+        <v>4126</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="s">
+        <v>4143</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>4077</v>
+        <v>4074</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>4147</v>
+        <v>4144</v>
       </c>
       <c r="D24" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="E24" t="n">
         <v>7689</v>
@@ -15684,48 +15610,46 @@
         <v>7689</v>
       </c>
       <c r="U24" t="s">
-        <v>4148</v>
+        <v>4145</v>
       </c>
       <c r="V24" t="n">
         <v>177365</v>
       </c>
       <c r="W24" t="s">
-        <v>4080</v>
+        <v>4077</v>
       </c>
       <c r="X24" t="b">
         <v>1</v>
       </c>
-      <c r="Y24"/>
-      <c r="Z24"/>
-      <c r="AA24" t="s">
-        <v>4081</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="Y24" t="s">
+        <v>4078</v>
+      </c>
+      <c r="Z24" t="n">
         <v>-0.230046077554706</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AA24" t="n">
         <v>0.102774340854425</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>19</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>4146</v>
       </c>
       <c r="AD24" t="s">
         <v>19</v>
       </c>
       <c r="AE24" t="s">
-        <v>4149</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG24" t="s">
-        <v>4149</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="s">
-        <v>4150</v>
+        <v>4146</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="s">
+        <v>4147</v>
       </c>
     </row>
   </sheetData>
@@ -15804,37 +15728,28 @@
         <v>4063</v>
       </c>
       <c r="V1" t="s">
-        <v>4151</v>
+        <v>41</v>
       </c>
       <c r="W1" t="s">
-        <v>4152</v>
+        <v>4067</v>
       </c>
       <c r="X1" t="s">
-        <v>4153</v>
+        <v>4068</v>
       </c>
       <c r="Y1" t="s">
-        <v>4154</v>
+        <v>4069</v>
       </c>
       <c r="Z1" t="s">
-        <v>4155</v>
+        <v>12</v>
       </c>
       <c r="AA1" t="s">
-        <v>4071</v>
+        <v>4070</v>
       </c>
       <c r="AB1" t="s">
-        <v>4072</v>
+        <v>4148</v>
       </c>
       <c r="AC1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD1" t="s">
         <v>4073</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>4156</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>4076</v>
       </c>
     </row>
     <row r="2">
@@ -15842,10 +15757,10 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>4157</v>
+        <v>4149</v>
       </c>
       <c r="C2" t="s">
-        <v>4093</v>
+        <v>4090</v>
       </c>
       <c r="D2" t="n">
         <v>7689</v>
@@ -15902,37 +15817,28 @@
         <v>11363</v>
       </c>
       <c r="V2" t="n">
-        <v>-20.3966453365704</v>
+        <v>-2.84447916797476</v>
       </c>
       <c r="W2" t="n">
-        <v>-17.2110375099997</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-15.2116864596859</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-10.4130888507221</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-12.9855845151858</v>
+        <v>0.181918518507475</v>
+      </c>
+      <c r="X2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>19</v>
       </c>
       <c r="AA2" t="s">
         <v>19</v>
       </c>
-      <c r="AB2" t="s">
-        <v>19</v>
+      <c r="AB2" t="n">
+        <v>0</v>
       </c>
       <c r="AC2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>4158</v>
+        <v>4150</v>
       </c>
     </row>
     <row r="3">
@@ -15940,10 +15846,10 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>4159</v>
+        <v>4151</v>
       </c>
       <c r="C3" t="s">
-        <v>4160</v>
+        <v>4152</v>
       </c>
       <c r="D3" t="n">
         <v>30041</v>
@@ -16000,37 +15906,28 @@
         <v>36803</v>
       </c>
       <c r="V3" t="n">
-        <v>4.64778052738578</v>
+        <v>0.666191460811144</v>
       </c>
       <c r="W3" t="n">
-        <v>0.750115882074461</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.20572502512759</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.535937670612629</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.940749507404908</v>
+        <v>0.264787962493797</v>
+      </c>
+      <c r="X3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>19</v>
       </c>
       <c r="AA3" t="s">
         <v>19</v>
       </c>
-      <c r="AB3" t="s">
-        <v>19</v>
+      <c r="AB3" t="n">
+        <v>0</v>
       </c>
       <c r="AC3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>4161</v>
+        <v>4153</v>
       </c>
     </row>
     <row r="4">
@@ -16038,10 +15935,10 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>4162</v>
+        <v>4154</v>
       </c>
       <c r="C4" t="s">
-        <v>4163</v>
+        <v>4155</v>
       </c>
       <c r="D4" t="n">
         <v>24134</v>
@@ -16098,37 +15995,28 @@
         <v>43471</v>
       </c>
       <c r="V4" t="n">
-        <v>2.62188038884115</v>
+        <v>0.219003536583554</v>
       </c>
       <c r="W4" t="n">
-        <v>2.57638125349544</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.0565541655578</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-0.28360782333674</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.588481600162203</v>
+        <v>0.137427879869313</v>
+      </c>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>19</v>
       </c>
       <c r="AA4" t="s">
         <v>19</v>
       </c>
-      <c r="AB4" t="s">
-        <v>19</v>
+      <c r="AB4" t="n">
+        <v>0.00296296296296296</v>
       </c>
       <c r="AC4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0.00296296296296296</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>4164</v>
+        <v>4156</v>
       </c>
     </row>
     <row r="5">
@@ -16136,10 +16024,10 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>4165</v>
+        <v>4157</v>
       </c>
       <c r="C5" t="s">
-        <v>4166</v>
+        <v>4158</v>
       </c>
       <c r="D5" t="n">
         <v>19095</v>
@@ -16196,37 +16084,28 @@
         <v>6426</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44733693667756</v>
+        <v>0.631977532397669</v>
       </c>
       <c r="W5" t="n">
-        <v>0.547512237618506</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.17558195115071</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.7160619962937</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.20520978988592</v>
+        <v>0.34450849464285</v>
+      </c>
+      <c r="X5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>19</v>
       </c>
       <c r="AA5" t="s">
         <v>19</v>
       </c>
-      <c r="AB5" t="s">
-        <v>19</v>
+      <c r="AB5" t="n">
+        <v>0.0052863436123348</v>
       </c>
       <c r="AC5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD5" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0.0052863436123348</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>4167</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="6">
@@ -16234,10 +16113,10 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>4168</v>
+        <v>4160</v>
       </c>
       <c r="C6" t="s">
-        <v>4169</v>
+        <v>4161</v>
       </c>
       <c r="D6" t="n">
         <v>30041</v>
@@ -16294,37 +16173,28 @@
         <v>44465</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.27240228886354</v>
+        <v>0.268019622294045</v>
       </c>
       <c r="W6" t="n">
-        <v>2.63853309727849</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.79513354231431</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.44300637733628</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>-0.337198930897762</v>
+        <v>0.214279195761509</v>
+      </c>
+      <c r="X6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>19</v>
       </c>
       <c r="AA6" t="s">
         <v>19</v>
       </c>
-      <c r="AB6" t="s">
-        <v>19</v>
+      <c r="AB6" t="n">
+        <v>0.0327948614985818</v>
       </c>
       <c r="AC6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AD6" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0.0327948614985818</v>
-      </c>
-      <c r="AF6" t="s">
-        <v>4170</v>
+        <v>4162</v>
       </c>
     </row>
   </sheetData>
@@ -16355,34 +16225,34 @@
         <v>28</v>
       </c>
       <c r="F1" t="s">
-        <v>4171</v>
+        <v>4163</v>
       </c>
       <c r="G1" t="s">
         <v>2602</v>
       </c>
       <c r="H1" t="s">
-        <v>4172</v>
+        <v>4164</v>
       </c>
       <c r="I1" t="s">
-        <v>4173</v>
+        <v>4165</v>
       </c>
       <c r="J1" t="s">
         <v>2629</v>
       </c>
       <c r="K1" t="s">
-        <v>4174</v>
+        <v>4166</v>
       </c>
       <c r="L1" t="s">
-        <v>4175</v>
+        <v>4167</v>
       </c>
       <c r="M1" t="s">
-        <v>4176</v>
+        <v>4168</v>
       </c>
       <c r="N1" t="s">
-        <v>4177</v>
+        <v>4169</v>
       </c>
       <c r="O1" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="P1" t="s">
         <v>4063</v>
@@ -16402,30 +16272,30 @@
         <v>483</v>
       </c>
       <c r="E2" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F2" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G2" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
       <c r="J2" t="s">
-        <v>4181</v>
+        <v>4173</v>
       </c>
       <c r="K2" t="s">
-        <v>4182</v>
+        <v>4174</v>
       </c>
       <c r="L2" t="s">
-        <v>4181</v>
+        <v>4173</v>
       </c>
       <c r="M2" t="s">
-        <v>4183</v>
+        <v>4175</v>
       </c>
       <c r="N2" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O2"/>
       <c r="P2" t="n">
@@ -16446,30 +16316,30 @@
         <v>528</v>
       </c>
       <c r="E3" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F3" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G3" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
       <c r="J3" t="s">
-        <v>4185</v>
+        <v>4177</v>
       </c>
       <c r="K3" t="s">
-        <v>4186</v>
+        <v>4178</v>
       </c>
       <c r="L3" t="s">
-        <v>4185</v>
+        <v>4177</v>
       </c>
       <c r="M3" t="s">
-        <v>4187</v>
+        <v>4179</v>
       </c>
       <c r="N3" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O3"/>
       <c r="P3" t="n">
@@ -16490,30 +16360,30 @@
         <v>1179</v>
       </c>
       <c r="E4" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F4" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G4" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
       <c r="J4" t="s">
-        <v>4189</v>
+        <v>4181</v>
       </c>
       <c r="K4" t="s">
-        <v>4190</v>
+        <v>4182</v>
       </c>
       <c r="L4" t="s">
-        <v>4189</v>
+        <v>4181</v>
       </c>
       <c r="M4" t="s">
-        <v>4191</v>
+        <v>4183</v>
       </c>
       <c r="N4" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O4"/>
       <c r="P4" t="n">
@@ -16534,30 +16404,30 @@
         <v>309</v>
       </c>
       <c r="E5" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F5" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G5" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
       <c r="J5" t="s">
-        <v>4192</v>
+        <v>4184</v>
       </c>
       <c r="K5" t="s">
-        <v>4193</v>
+        <v>4185</v>
       </c>
       <c r="L5" t="s">
-        <v>4192</v>
+        <v>4184</v>
       </c>
       <c r="M5" t="s">
-        <v>4183</v>
+        <v>4175</v>
       </c>
       <c r="N5" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O5"/>
       <c r="P5" t="n">
@@ -16578,30 +16448,30 @@
         <v>525</v>
       </c>
       <c r="E6" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F6" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G6" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
       <c r="J6" t="s">
-        <v>4194</v>
+        <v>4186</v>
       </c>
       <c r="K6" t="s">
-        <v>4195</v>
+        <v>4187</v>
       </c>
       <c r="L6" t="s">
-        <v>4194</v>
+        <v>4186</v>
       </c>
       <c r="M6" t="s">
-        <v>4183</v>
+        <v>4175</v>
       </c>
       <c r="N6" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O6"/>
       <c r="P6" t="n">
@@ -16622,33 +16492,33 @@
         <v>1140</v>
       </c>
       <c r="E7" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F7" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G7" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H7"/>
       <c r="I7"/>
       <c r="J7" t="s">
-        <v>4165</v>
+        <v>4157</v>
       </c>
       <c r="K7" t="s">
-        <v>4196</v>
+        <v>4188</v>
       </c>
       <c r="L7" t="s">
-        <v>4165</v>
+        <v>4157</v>
       </c>
       <c r="M7" t="s">
-        <v>4197</v>
+        <v>4189</v>
       </c>
       <c r="N7" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O7" t="s">
-        <v>4167</v>
+        <v>4159</v>
       </c>
       <c r="P7" t="n">
         <v>6996</v>
@@ -16668,33 +16538,33 @@
         <v>678</v>
       </c>
       <c r="E8" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F8" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G8" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H8"/>
       <c r="I8"/>
       <c r="J8" t="s">
-        <v>4199</v>
+        <v>4191</v>
       </c>
       <c r="K8" t="s">
-        <v>4200</v>
+        <v>4192</v>
       </c>
       <c r="L8" t="s">
-        <v>4199</v>
+        <v>4191</v>
       </c>
       <c r="M8" t="s">
-        <v>4201</v>
+        <v>4193</v>
       </c>
       <c r="N8" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O8" t="s">
-        <v>4202</v>
+        <v>4194</v>
       </c>
       <c r="P8" t="n">
         <v>9884</v>
@@ -16714,33 +16584,33 @@
         <v>669</v>
       </c>
       <c r="E9" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F9" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G9" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
       <c r="J9" t="s">
-        <v>4203</v>
+        <v>4195</v>
       </c>
       <c r="K9" t="s">
-        <v>4204</v>
+        <v>4196</v>
       </c>
       <c r="L9" t="s">
-        <v>4203</v>
+        <v>4195</v>
       </c>
       <c r="M9" t="s">
-        <v>4187</v>
+        <v>4179</v>
       </c>
       <c r="N9" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O9" t="s">
-        <v>4205</v>
+        <v>4197</v>
       </c>
       <c r="P9" t="n">
         <v>10635</v>
@@ -16760,33 +16630,33 @@
         <v>897</v>
       </c>
       <c r="E10" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F10" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G10" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H10"/>
       <c r="I10"/>
       <c r="J10" t="s">
-        <v>4157</v>
+        <v>4149</v>
       </c>
       <c r="K10" t="s">
-        <v>4206</v>
+        <v>4198</v>
       </c>
       <c r="L10" t="s">
-        <v>4157</v>
+        <v>4149</v>
       </c>
       <c r="M10" t="s">
-        <v>4207</v>
+        <v>4199</v>
       </c>
       <c r="N10" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O10" t="s">
-        <v>4158</v>
+        <v>4150</v>
       </c>
       <c r="P10" t="n">
         <v>11811</v>
@@ -16806,33 +16676,33 @@
         <v>1023</v>
       </c>
       <c r="E11" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F11" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G11" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
       <c r="J11" t="s">
-        <v>4208</v>
+        <v>4200</v>
       </c>
       <c r="K11" t="s">
-        <v>4209</v>
+        <v>4201</v>
       </c>
       <c r="L11" t="s">
-        <v>4208</v>
+        <v>4200</v>
       </c>
       <c r="M11" t="s">
-        <v>4210</v>
+        <v>4202</v>
       </c>
       <c r="N11" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O11" t="s">
-        <v>4211</v>
+        <v>4203</v>
       </c>
       <c r="P11" t="n">
         <v>13440</v>
@@ -16852,33 +16722,33 @@
         <v>1677</v>
       </c>
       <c r="E12" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F12" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G12" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>4212</v>
+        <v>4204</v>
       </c>
       <c r="K12" t="s">
-        <v>4213</v>
+        <v>4205</v>
       </c>
       <c r="L12" t="s">
-        <v>4212</v>
+        <v>4204</v>
       </c>
       <c r="M12" t="s">
-        <v>4214</v>
+        <v>4206</v>
       </c>
       <c r="N12" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O12" t="s">
-        <v>4215</v>
+        <v>4207</v>
       </c>
       <c r="P12" t="n">
         <v>17842</v>
@@ -16898,33 +16768,33 @@
         <v>1941</v>
       </c>
       <c r="E13" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F13" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G13" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H13"/>
       <c r="I13"/>
       <c r="J13" t="s">
-        <v>4216</v>
+        <v>4208</v>
       </c>
       <c r="K13" t="s">
-        <v>4217</v>
+        <v>4209</v>
       </c>
       <c r="L13" t="s">
-        <v>4216</v>
+        <v>4208</v>
       </c>
       <c r="M13" t="s">
-        <v>4218</v>
+        <v>4210</v>
       </c>
       <c r="N13" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O13" t="s">
-        <v>4219</v>
+        <v>4211</v>
       </c>
       <c r="P13" t="n">
         <v>21817</v>
@@ -16944,33 +16814,33 @@
         <v>1776</v>
       </c>
       <c r="E14" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F14" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G14" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H14"/>
       <c r="I14"/>
       <c r="J14" t="s">
-        <v>4220</v>
+        <v>4212</v>
       </c>
       <c r="K14" t="s">
-        <v>4221</v>
+        <v>4213</v>
       </c>
       <c r="L14" t="s">
-        <v>4220</v>
+        <v>4212</v>
       </c>
       <c r="M14" t="s">
-        <v>4222</v>
+        <v>4214</v>
       </c>
       <c r="N14" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O14" t="s">
-        <v>4223</v>
+        <v>4215</v>
       </c>
       <c r="P14" t="n">
         <v>24310</v>
@@ -16990,33 +16860,33 @@
         <v>1398</v>
       </c>
       <c r="E15" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F15" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G15" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>4224</v>
+        <v>4216</v>
       </c>
       <c r="K15" t="s">
-        <v>4225</v>
+        <v>4217</v>
       </c>
       <c r="L15" t="s">
-        <v>4224</v>
+        <v>4216</v>
       </c>
       <c r="M15" t="s">
-        <v>4226</v>
+        <v>4218</v>
       </c>
       <c r="N15" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O15" t="s">
-        <v>4227</v>
+        <v>4219</v>
       </c>
       <c r="P15" t="n">
         <v>28930</v>
@@ -17036,30 +16906,30 @@
         <v>483</v>
       </c>
       <c r="E16" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F16" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G16" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16" t="s">
-        <v>4228</v>
+        <v>4220</v>
       </c>
       <c r="K16" t="s">
-        <v>4229</v>
+        <v>4221</v>
       </c>
       <c r="L16" t="s">
-        <v>4228</v>
+        <v>4220</v>
       </c>
       <c r="M16" t="s">
-        <v>4183</v>
+        <v>4175</v>
       </c>
       <c r="N16" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O16"/>
       <c r="P16" t="n">
@@ -17080,33 +16950,33 @@
         <v>2577</v>
       </c>
       <c r="E17" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F17" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G17" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17" t="s">
-        <v>4230</v>
+        <v>4222</v>
       </c>
       <c r="K17" t="s">
-        <v>4231</v>
+        <v>4223</v>
       </c>
       <c r="L17" t="s">
-        <v>4230</v>
+        <v>4222</v>
       </c>
       <c r="M17" t="s">
-        <v>4232</v>
+        <v>4224</v>
       </c>
       <c r="N17" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O17" t="s">
-        <v>4233</v>
+        <v>4225</v>
       </c>
       <c r="P17" t="n">
         <v>34560</v>
@@ -17126,33 +16996,33 @@
         <v>1872</v>
       </c>
       <c r="E18" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F18" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G18" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18" t="s">
-        <v>4159</v>
+        <v>4151</v>
       </c>
       <c r="K18" t="s">
-        <v>4234</v>
+        <v>4226</v>
       </c>
       <c r="L18" t="s">
-        <v>4159</v>
+        <v>4151</v>
       </c>
       <c r="M18" t="s">
-        <v>4235</v>
+        <v>4227</v>
       </c>
       <c r="N18" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O18" t="s">
-        <v>4161</v>
+        <v>4153</v>
       </c>
       <c r="P18" t="n">
         <v>37738</v>
@@ -17172,33 +17042,33 @@
         <v>1338</v>
       </c>
       <c r="E19" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F19" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G19" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>4236</v>
+        <v>4228</v>
       </c>
       <c r="K19" t="s">
-        <v>4237</v>
+        <v>4229</v>
       </c>
       <c r="L19" t="s">
-        <v>4236</v>
+        <v>4228</v>
       </c>
       <c r="M19" t="s">
-        <v>4238</v>
+        <v>4230</v>
       </c>
       <c r="N19" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O19" t="s">
-        <v>4239</v>
+        <v>4231</v>
       </c>
       <c r="P19" t="n">
         <v>39512</v>
@@ -17218,33 +17088,33 @@
         <v>2145</v>
       </c>
       <c r="E20" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F20" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G20" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20" t="s">
-        <v>4240</v>
+        <v>4232</v>
       </c>
       <c r="K20" t="s">
-        <v>4241</v>
+        <v>4233</v>
       </c>
       <c r="L20" t="s">
-        <v>4240</v>
+        <v>4232</v>
       </c>
       <c r="M20" t="s">
-        <v>4242</v>
+        <v>4234</v>
       </c>
       <c r="N20" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O20" t="s">
-        <v>4243</v>
+        <v>4235</v>
       </c>
       <c r="P20" t="n">
         <v>41493</v>
@@ -17264,33 +17134,33 @@
         <v>624</v>
       </c>
       <c r="E21" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F21" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G21" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21" t="s">
-        <v>4244</v>
+        <v>4236</v>
       </c>
       <c r="K21" t="s">
-        <v>4245</v>
+        <v>4237</v>
       </c>
       <c r="L21" t="s">
-        <v>4244</v>
+        <v>4236</v>
       </c>
       <c r="M21" t="s">
-        <v>4246</v>
+        <v>4238</v>
       </c>
       <c r="N21" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O21" t="s">
-        <v>4247</v>
+        <v>4239</v>
       </c>
       <c r="P21" t="n">
         <v>43126</v>
@@ -17310,33 +17180,33 @@
         <v>765</v>
       </c>
       <c r="E22" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F22" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G22" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H22"/>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>4162</v>
+        <v>4154</v>
       </c>
       <c r="K22" t="s">
-        <v>4248</v>
+        <v>4240</v>
       </c>
       <c r="L22" t="s">
-        <v>4162</v>
+        <v>4154</v>
       </c>
       <c r="M22" t="s">
-        <v>4249</v>
+        <v>4241</v>
       </c>
       <c r="N22" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O22" t="s">
-        <v>4164</v>
+        <v>4156</v>
       </c>
       <c r="P22" t="n">
         <v>44010</v>
@@ -17356,33 +17226,33 @@
         <v>906</v>
       </c>
       <c r="E23" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F23" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G23" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H23"/>
       <c r="I23"/>
       <c r="J23" t="s">
-        <v>4168</v>
+        <v>4160</v>
       </c>
       <c r="K23" t="s">
-        <v>4250</v>
+        <v>4242</v>
       </c>
       <c r="L23" t="s">
-        <v>4168</v>
+        <v>4160</v>
       </c>
       <c r="M23" t="s">
-        <v>4251</v>
+        <v>4243</v>
       </c>
       <c r="N23" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O23" t="s">
-        <v>4170</v>
+        <v>4162</v>
       </c>
       <c r="P23" t="n">
         <v>45108</v>
@@ -17402,33 +17272,33 @@
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F24" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G24" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H24"/>
       <c r="I24"/>
       <c r="J24" t="s">
-        <v>4252</v>
+        <v>4244</v>
       </c>
       <c r="K24" t="s">
-        <v>4253</v>
+        <v>4245</v>
       </c>
       <c r="L24" t="s">
-        <v>4252</v>
+        <v>4244</v>
       </c>
       <c r="M24" t="s">
-        <v>4254</v>
+        <v>4246</v>
       </c>
       <c r="N24" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O24" t="s">
-        <v>4255</v>
+        <v>4247</v>
       </c>
       <c r="P24" t="n">
         <v>46732</v>
@@ -17448,30 +17318,30 @@
         <v>192</v>
       </c>
       <c r="E25" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F25" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G25" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H25"/>
       <c r="I25"/>
       <c r="J25" t="s">
-        <v>4256</v>
+        <v>4248</v>
       </c>
       <c r="K25" t="s">
-        <v>4257</v>
+        <v>4249</v>
       </c>
       <c r="L25" t="s">
-        <v>4256</v>
+        <v>4248</v>
       </c>
       <c r="M25" t="s">
-        <v>4183</v>
+        <v>4175</v>
       </c>
       <c r="N25" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O25"/>
       <c r="P25" t="n">
@@ -17492,33 +17362,33 @@
         <v>1869</v>
       </c>
       <c r="E26" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F26" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G26" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H26"/>
       <c r="I26"/>
       <c r="J26" t="s">
-        <v>4258</v>
+        <v>4250</v>
       </c>
       <c r="K26" t="s">
-        <v>4259</v>
+        <v>4251</v>
       </c>
       <c r="L26" t="s">
-        <v>4258</v>
+        <v>4250</v>
       </c>
       <c r="M26" t="s">
-        <v>4260</v>
+        <v>4252</v>
       </c>
       <c r="N26" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O26" t="s">
-        <v>4261</v>
+        <v>4253</v>
       </c>
       <c r="P26" t="n">
         <v>50073</v>
@@ -17538,30 +17408,30 @@
         <v>1623</v>
       </c>
       <c r="E27" t="s">
-        <v>4179</v>
+        <v>4171</v>
       </c>
       <c r="F27" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G27" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H27"/>
       <c r="I27"/>
       <c r="J27" t="s">
-        <v>4262</v>
+        <v>4254</v>
       </c>
       <c r="K27" t="s">
-        <v>4263</v>
+        <v>4255</v>
       </c>
       <c r="L27" t="s">
-        <v>4262</v>
+        <v>4254</v>
       </c>
       <c r="M27" t="s">
-        <v>4264</v>
+        <v>4256</v>
       </c>
       <c r="N27" t="s">
-        <v>4184</v>
+        <v>4176</v>
       </c>
       <c r="O27"/>
       <c r="P27" t="n">
@@ -17582,33 +17452,33 @@
         <v>1437</v>
       </c>
       <c r="E28" t="s">
-        <v>4188</v>
+        <v>4180</v>
       </c>
       <c r="F28" t="s">
-        <v>4180</v>
+        <v>4172</v>
       </c>
       <c r="G28" t="s">
-        <v>4178</v>
+        <v>4170</v>
       </c>
       <c r="H28"/>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>4265</v>
+        <v>4257</v>
       </c>
       <c r="K28" t="s">
-        <v>4266</v>
+        <v>4258</v>
       </c>
       <c r="L28" t="s">
-        <v>4265</v>
+        <v>4257</v>
       </c>
       <c r="M28" t="s">
-        <v>4267</v>
+        <v>4259</v>
       </c>
       <c r="N28" t="s">
-        <v>4198</v>
+        <v>4190</v>
       </c>
       <c r="O28" t="s">
-        <v>4268</v>
+        <v>4260</v>
       </c>
       <c r="P28" t="n">
         <v>53978</v>
